--- a/data/002594_比亚迪_财务数据.xlsx
+++ b/data/002594_比亚迪_财务数据.xlsx
@@ -11638,7 +11638,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -19306,7 +19306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19336,8 +19336,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19384,22 +19382,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -19409,75 +19407,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -19512,57 +19500,51 @@
       </c>
       <c r="I2" s="4" t="inlineStr"/>
       <c r="J2" s="3" t="n">
-        <v>1.181202315102029</v>
-      </c>
-      <c r="K2" s="3" t="n">
         <v>61.80490932026387</v>
       </c>
+      <c r="K2" s="6" t="n">
+        <v>0.9990040603692638</v>
+      </c>
       <c r="L2" s="6" t="n">
-        <v>0.9990040603692638</v>
-      </c>
-      <c r="M2" s="6" t="n">
         <v>0.7771138180239536</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>161.816672381743</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>2.149802555578641</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>167.4572388361044</v>
-      </c>
-      <c r="P2" s="3" t="n">
         <v>5.566780527103234</v>
       </c>
+      <c r="P2" s="6" t="n">
+        <v>0.713236946047108</v>
+      </c>
       <c r="Q2" s="3" t="n">
-        <v>64.6693359379361</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0.713236946047108</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.322469286809816</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="6" t="n">
+        <v>-0.3368605762177163</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>-14899000000</v>
+      </c>
       <c r="X2" s="6" t="n">
-        <v>-0.3368605762177163</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>-14899000000</v>
-      </c>
-      <c r="Z2" s="6" t="n">
         <v>0.8464386057728406</v>
       </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>1.446948387662539</v>
+      </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.446948387662539</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19599,63 +19581,57 @@
         <v>3.530662815819469</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2.185155560367814</v>
-      </c>
-      <c r="K3" s="3" t="n">
         <v>66.33501591811296</v>
       </c>
+      <c r="K3" s="6" t="n">
+        <v>0.9779707991656903</v>
+      </c>
       <c r="L3" s="6" t="n">
-        <v>0.9779707991656903</v>
-      </c>
-      <c r="M3" s="6" t="n">
         <v>0.7886987247254682</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>197.0445485931584</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>1.98001013235624</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>181.8172513953728</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>5.442716544522295</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.6554736021289105</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>66.14344088198278</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.6554736021289105</v>
-      </c>
+        <v>1.170819813844487</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.170819813844487</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>2.362718730918684</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-10.27508698886061</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>2.362718730918684</v>
+        <v>22.76678316134858</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>-10.27508698886061</v>
+        <v>1.338028398173172</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>22.76678316134858</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>1.338028398173172</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-8198000000.000001</v>
       </c>
-      <c r="Z3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>0.8907261996545107</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>1.209180540078953</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.209180540078953</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19692,63 +19668,57 @@
         <v>3.836354804136386</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.026328812535789</v>
-      </c>
-      <c r="K4" s="3" t="n">
         <v>68.8062455350489</v>
       </c>
+      <c r="K4" s="6" t="n">
+        <v>0.9883502474929011</v>
+      </c>
       <c r="L4" s="6" t="n">
-        <v>0.9883502474929011</v>
-      </c>
-      <c r="M4" s="6" t="n">
         <v>0.762475443728607</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>220.5769927834711</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>2.405347001054209</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>149.6665553212157</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>5.496853494361838</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0.6979617731505084</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>65.49201290688474</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0.6979617731505084</v>
-      </c>
+        <v>1.193737414809886</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>1.193737414809886</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>22.79193024590675</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-27.67461280765095</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>22.79193024590675</v>
+        <v>9.248788595107216</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-27.67461280765095</v>
+        <v>3.521462417815906</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>9.248788595107216</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>3.521462417815906</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>-5319000000</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.798225626697233</v>
       </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1.23446765823042</v>
+      </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>1.23446765823042</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19785,63 +19755,57 @@
         <v>4.406949342916701</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.359532527239257</v>
-      </c>
-      <c r="K5" s="3" t="n">
         <v>68.00175831365453</v>
       </c>
+      <c r="K5" s="6" t="n">
+        <v>0.9901693063899508</v>
+      </c>
       <c r="L5" s="6" t="n">
-        <v>0.9901693063899508</v>
-      </c>
-      <c r="M5" s="6" t="n">
         <v>0.7534550907626656</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>212.5205667641092</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>2.740640713166985</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>131.3561453971094</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>4.840475588609302</v>
       </c>
+      <c r="P5" s="6" t="n">
+        <v>0.6547117753637116</v>
+      </c>
       <c r="Q5" s="3" t="n">
-        <v>74.37285725542316</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0.6547117753637116</v>
-      </c>
+        <v>1.149875532230914</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.149875532230914</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="3" t="n">
         <v>-1.78093054332897</v>
       </c>
+      <c r="T5" s="3" t="n">
+        <v>-40.41782884112308</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0.5504417410611037</v>
+      </c>
       <c r="V5" s="3" t="n">
-        <v>-40.41782884112308</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>0.5504417410611037</v>
-      </c>
-      <c r="X5" s="3" t="n">
         <v>6.957052788366558</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="W5" s="3" t="n">
         <v>-5886000000</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.8389481691439318</v>
       </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>1.208569972884745</v>
+      </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>1.208569972884745</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19878,63 +19842,57 @@
         <v>4.76690361928772</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.402723805167728</v>
+        <v>67.93604521010661</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>67.93604521010661</v>
-      </c>
-      <c r="L6" s="3" t="n">
         <v>1.048613655795774</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="L6" s="6" t="n">
         <v>0.7536244139395477</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>211.8766872498216</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>3.67816068115091</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>97.87500634348434</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>5.231371015306839</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0.789583450772578</v>
+      </c>
       <c r="Q6" s="3" t="n">
-        <v>68.81561237898259</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0.789583450772578</v>
-      </c>
+        <v>1.432916302179602</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>1.432916302179602</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>22.5923764595274</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>183.8305274966645</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>22.5923764595274</v>
+        <v>2.747365085206653</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>183.8305274966645</v>
+        <v>7.54793469796871</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>2.747365085206653</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>7.54793469796871</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>33619000000</v>
       </c>
-      <c r="Z6" s="6" t="n">
+      <c r="X6" s="6" t="n">
         <v>0.8854983691937067</v>
       </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>1.458679048170673</v>
+      </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.458679048170673</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19970,64 +19928,58 @@
       <c r="I7" s="3" t="n">
         <v>3.697087746251725</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>0.8267360042901347</v>
-      </c>
-      <c r="K7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>64.75623774426938</v>
       </c>
+      <c r="K7" s="6" t="n">
+        <v>0.9696796338672768</v>
+      </c>
       <c r="L7" s="6" t="n">
-        <v>0.9696796338672768</v>
-      </c>
-      <c r="M7" s="6" t="n">
         <v>0.7165915565310792</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>183.7381527953647</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>5.580244362115481</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>64.51330383379901</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>5.688280798919078</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.8701437206746417</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>63.28801490749356</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.8701437206746417</v>
-      </c>
+        <v>1.556577030408872</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.556577030408872</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>38.02399870634108</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-34.03241755893742</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>38.02399870634108</v>
+        <v>47.14178402821652</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>-34.03241755893742</v>
+        <v>16.50179241825479</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>47.14178402821652</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>16.50179241825479</v>
-      </c>
-      <c r="Y7" s="3" t="n">
         <v>28122999999.99999</v>
       </c>
-      <c r="Z7" s="6" t="n">
+      <c r="X7" s="6" t="n">
         <v>0.9376503855247833</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>1.256855350008407</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>1.256855350008407</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20063,64 +20015,58 @@
       <c r="I8" s="3" t="n">
         <v>4.399006052518881</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.3815390692889944</v>
-      </c>
-      <c r="K8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>75.42020933015566</v>
       </c>
+      <c r="K8" s="6" t="n">
+        <v>0.7223867164649237</v>
+      </c>
       <c r="L8" s="6" t="n">
-        <v>0.7223867164649237</v>
-      </c>
-      <c r="M8" s="6" t="n">
         <v>0.4850740224092157</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>306.8382898097042</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>11.29638474140572</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>31.86860294165244</v>
+        <v>6.552029723506068</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>6.552029723506068</v>
+        <v>1.074059313029592</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>54.94480568494122</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>1.074059313029592</v>
-      </c>
+        <v>2.084276456450257</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>2.084276456450257</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>96.19502920748148</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>346.4813803763095</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>96.19502920748148</v>
+        <v>66.96903103658121</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>346.4813803763095</v>
+        <v>7.951062670890432</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>66.96903103658121</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>7.951062670890432</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>43381000000</v>
       </c>
-      <c r="Z8" s="6" t="n">
+      <c r="X8" s="6" t="n">
         <v>0.9744101807516277</v>
       </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>1.1144516957965</v>
+      </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>1.1144516957965</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20156,64 +20102,58 @@
       <c r="I9" s="3" t="n">
         <v>6.57046922964544</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.244870729295737</v>
-      </c>
-      <c r="K9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>77.85851772060251</v>
       </c>
+      <c r="K9" s="6" t="n">
+        <v>0.665953221195282</v>
+      </c>
       <c r="L9" s="6" t="n">
-        <v>0.665953221195282</v>
-      </c>
-      <c r="M9" s="6" t="n">
         <v>0.4726903213149733</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>351.640945886669</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>11.96328190358909</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>30.09207698198575</v>
+        <v>6.807381187643899</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.807381187643899</v>
+        <v>1.026607694333348</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>52.88377278672704</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>1.026607694333348</v>
-      </c>
+        <v>2.218779219965926</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>2.218779219965926</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>42.03519598087665</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>76.95413519843839</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>42.03519598087665</v>
+        <v>37.59904102571373</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>76.95413519843839</v>
+        <v>5.414899851869907</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>37.59904102571373</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>5.414899851869907</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>47631000000</v>
       </c>
-      <c r="Z9" s="6" t="n">
+      <c r="X9" s="6" t="n">
         <v>0.9508391180743502</v>
       </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>1.132701843032951</v>
+      </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>1.132701843032951</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20249,64 +20189,58 @@
       <c r="I10" s="3" t="n">
         <v>6.845267912581746</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>0.1565052319902914</v>
-      </c>
-      <c r="K10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>74.63630839618259</v>
       </c>
+      <c r="K10" s="6" t="n">
+        <v>0.747143562809359</v>
+      </c>
       <c r="L10" s="6" t="n">
-        <v>0.747143562809359</v>
-      </c>
-      <c r="M10" s="6" t="n">
         <v>0.5131929393025998</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>294.2643742953776</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>12.5172545403294</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>28.76030033903316</v>
+        <v>7.244897939748568</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>7.244897939748568</v>
+        <v>1.062410732351542</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>49.6901409783688</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>1.062410732351542</v>
-      </c>
+        <v>2.310422302595686</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>2.310422302595686</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>29.01920062957585</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>32.68200332630702</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>29.01920062957585</v>
+        <v>15.27603642421139</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>32.68200332630702</v>
+        <v>3.20895913574945</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>15.27603642421139</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>3.20895913574945</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>36094000000</v>
       </c>
-      <c r="Z10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.9964541934177779</v>
       </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>1.411386787108816</v>
+      </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.411386787108816</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -20342,64 +20276,58 @@
       <c r="I11" s="3" t="n">
         <v>7.211521400662839</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.08076844563168138</v>
-      </c>
-      <c r="K11" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>70.74457130571555</v>
       </c>
+      <c r="K11" s="6" t="n">
+        <v>0.7929708763563318</v>
+      </c>
       <c r="L11" s="6" t="n">
-        <v>0.7929708763563318</v>
-      </c>
-      <c r="M11" s="6" t="n">
         <v>0.4974842619612297</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>241.8169018987464</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>16.19199544832031</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>22.23320783093136</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>6.119689943684001</v>
       </c>
+      <c r="P11" s="6" t="n">
+        <v>0.9645152775561668</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>58.82650972726946</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.9645152775561668</v>
-      </c>
+        <v>2.166904635868686</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>2.166904635868686</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>3.456751786995706</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-18.82079756775642</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>3.456751786995706</v>
+        <v>12.81333135892236</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-18.82079756775642</v>
+        <v>1.751619439350266</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>12.81333135892236</v>
+        <v>-97672000000</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.751619439350266</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>-97672000000</v>
+        <v>1.021456211279298</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.021456211279298</v>
+        <v>1.38034942999664</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.38034942999664</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>

--- a/data/002594_比亚迪_财务数据.xlsx
+++ b/data/002594_比亚迪_财务数据.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务分析指标" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量校验" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并报表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40536,4 +40537,2123 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>营业利润率</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>净利润率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>净资产收益率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>存货周转率</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总资产周转率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>应收账款周转率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>流动比率</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>速动比率</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>利息保障倍数</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>货币资金占比</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>营业收入增长率</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>营业利润增长率</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>净利润增长率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2016Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0561578076914715</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05343193504126423</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0442511742647255</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.02016923314010693</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.130629030353136</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1576918807355496</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6295953382268502</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8076357367663572</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5414445902987554</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6712831755877582</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.03484662139279539</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.8039504437213814</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.8147066073981277</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.8361963440955968</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.06437688551602228</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.06201052223753445</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.0549297195645831</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.06653013396143088</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.585347759267228</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3842812076549215</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.785803420671024</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8037558044250205</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5810024583447145</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6813816897359017</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0449254528278638</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.215874669901727</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.571637081595749</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.750602130461229</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2016Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.06547646570040111</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.06102983346060368</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0545573018082005</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.08581392788973852</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.021115819960398</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5694913146026543</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.361456167383019</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.056774522751831</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7845779805498858</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5920746094800036</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05666646754875899</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6195438153850876</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5939309292782453</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.608563477621304</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017年报</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.04287775836823859</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.05108404119382784</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.04642354561881314</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.07703705527980904</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.382749269898582</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6788903510318149</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.466976498264738</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9779707991656904</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7806127794127451</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.309467425312771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6633501591811296</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05560390569290114</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4549164473262168</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.217814428033259</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2380080727133376</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0397712397400416</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.03922885994570596</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.03712633643284103</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01132274192794729</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.09312275862069</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1297442428912692</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4518617328481101</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.058728014518264</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.821182474381541</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6150171534792176</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06217623662233643</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.8012916280499001</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.8474062992844906</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.8410868069057641</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.04429073399210537</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.05700918545082638</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04807452486905563</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.03293503464755078</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.442426771832265</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3001898747254725</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.025890913646614</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.064816949760459</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8290164732405912</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.415409914100872</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.628132825966761</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05659739161544216</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.139947813703398</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.109870690490494</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.770997202335397</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.04581799481813875</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.05499270656180852</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04682459681850683</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0523098185089059</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.686144738217159</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4643107362550752</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.505654281263046</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.005668698497467</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7811860493111109</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.405102228542595</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6425865669467243</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0532999854305279</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6415802409882205</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5835157049945103</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5988994823946281</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018年报</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02359888442945779</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0326151978490098</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02734382385714037</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0508722518549693</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.466211570745986</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.723935813904297</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.576335555313438</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9883502474929012</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7593957227050073</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.360082930634732</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.688062455350489</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.06708091133827754</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7590912272541201</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04328577366648867</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.02724388323332017</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2018Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.006936818559142743</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01007075676203377</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01067772838595876</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001858302716922937</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9750710483050185</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1313497864161182</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4870606129219622</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9365237084978203</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7094466972813779</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.364275750335578</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6696742377646956</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.04471267902644759</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.8097910827633482</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.9412682471426955</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.9257236601050618</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.0004106300667412466</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01810836859126888</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01614674023142354</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.008769727810217643</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.177771944282527</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2900479119854952</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.070979252318577</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9400589584015723</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.727447571535354</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.684730677325334</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6896605801450101</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0545068662864551</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.189016178431467</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.936100607724605</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.310205534165465</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2018Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.01051296987864625</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.02585678482696471</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0241191280966076</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02809561745657933</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.312734893520957</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4641636181061802</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.259269843595473</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9592292819298084</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7205058883597131</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.005462200297867</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6884825202490266</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0734118308451496</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.64320956260585</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.346324897892584</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.454537656642966</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019年报</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.01662255794205481</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.01810172801199525</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01658745498411626</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02902616840912973</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.67501002995962</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.658870524822695</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.592727997889096</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9901693063899508</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7500948819298522</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.663039329794314</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6800175831365454</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.06465891781928215</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4355655140495434</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.005005713302193016</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.01271811129873368</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.03514599058853762</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0334775700894179</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.02931935538382895</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.01323761178745156</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.077222230409314</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1536454718760457</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6779064034449975</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.018430549579847</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7636868123666442</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.281625712657865</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6874352448874895</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.07002605293070323</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.7627645107498229</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.5612536154665855</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.5806715601855151</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.02529934301866699</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0287708000977675</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.02650680285460648</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.02569916961130742</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.135620379831578</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.311895989968652</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.287658808303567</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.020214381420277</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.7669941938365342</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.117205018861633</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6887367199535823</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05563614173385887</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.052007498256589</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.7635060541661574</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8551621446105051</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.01709718904659219</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.02191119831141158</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.02019624501543069</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.02773821039370634</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.317840148230765</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4712886952153711</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.892942397708014</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.023238545734558</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7681187320096071</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.822239340975977</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6848344818540454</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.05516430740669741</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5087707479945529</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.1490460798248943</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1495729555070477</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020年报</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.04845102728877404</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.04524825975882365</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03840390596819208</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.07448400999155644</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.056598469552234</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7844730702855154</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.509978504987112</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.048613655795774</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.746821884601291</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.268317668122906</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6793604521010661</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.07185959396468955</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6690971182314915</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.446810114858436</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.173849828587834</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.005509452885279709</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0190312879887138</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0163613747400595</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.001983220206181936</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6796723057106054</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1003034915133289</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4873459471507467</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.005476603119584</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7345580589254767</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.415194117118825</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6720369141370066</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.06605770185459049</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.8743369594127668</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.9471464863466554</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.9464632555936909</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.04901763030340356</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0487269008508109</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.03939347720788525</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02850458235813551</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.106704977756622</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3110701364270859</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.45002422978754</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.073873838322054</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7878988180975118</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.70229303393935</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.659920257442976</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.06699690339816633</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.074566499896181</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6.87198938340436</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6.40267045172191</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0555754110640132</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.05522916188932342</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.04667442493086228</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.05703875748790656</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.268771137146341</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5325218755942044</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.536257845611408</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.079174510353667</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7387351303720912</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.368367498599472</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6551811747010909</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.06698204767300647</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.7358256169373194</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.9674592952872048</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.05665171478164</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021年报</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.01637835094776297</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.02143027979309658</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0183548720277667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.03933462072528821</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.576601064945966</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8775948426546808</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.751603799944118</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9696796338672768</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.7047004156353617</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.428124354569673</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6475623774426938</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1705896274257894</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.058055381262437</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.2014236475555108</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.1906629121818996</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.01207502765243251</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.01576897937793669</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.01246715416004533</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.002694211592705891</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.023049299599591</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1577906203748078</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.119293149113945</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.240661166228921</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8967693435669937</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.183408120186226</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.6023110642424025</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1339362714651486</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.8103478357404155</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.8604488090653006</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.8711828246454864</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.01703184449867634</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.02438499472962654</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.01992367310921226</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.01445444692145681</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.366555072847682</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4069301167705423</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.424354135268149</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.14905218961545</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.7833334815908626</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.173368140068999</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5994257385764598</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.09775454810561027</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.217156556861893</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.428589108910891</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.54322260748417</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.01667992057818912</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.02664597540319581</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0227046591529287</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0298437276686191</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.552169210673633</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6116504393835992</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.862474774211569</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.026826907451762</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7287846994072221</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.50683406574751</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6379630034026705</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1436308122337321</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.5975322549056283</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7456557051582862</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.8205189943952051</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022年报</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.05393875571591311</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.05079891228290973</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.04177021524292157</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1718073601686813</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.697282807204981</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.13731560822934</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11.15552724689913</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7223867164649237</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4604028858989935</v>
+      </c>
+      <c r="K25" t="n">
+        <v>17.36481103050101</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.7542020933015567</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1042216332125841</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.920681507218169</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.568099551487906</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4.37323614465214</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.01822501501492291</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.01588047979216219</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.01364021663389334</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.007815462552084844</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9899999245510789</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1648102129023905</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.81041640139252</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9188802852561397</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6223890201704785</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.144651180708039</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6676737922377741</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1330351905233479</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.8424159672354403</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.9507369363747787</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.9485403574664271</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.03348091099889394</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.030689863460227</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.02611518335119746</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.03736247622808567</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.630657172805147</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.454308869908313</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.174374345186951</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8377414766209333</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5645023631441288</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8.08170569525222</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.6928973848292926</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1291715687266399</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.253749869903091</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.355490305460905</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.314967471558184</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.04775282532718039</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.04514723823080396</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.03731346085352915</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.09352477614338876</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.90150755337874</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6933355616739231</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7.222021745288745</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7520520085522084</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4756731387647969</v>
+      </c>
+      <c r="K28" t="n">
+        <v>12.71018440194605</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.7359084627819185</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1054170156558298</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.777390155156672</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.614682755690251</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.539540966801046</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年报</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.05750180826371565</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.06326103883448404</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.05203930099381129</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2489666257811076</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.047037241173842</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.089395537444643</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12.18842410506506</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.665953221195282</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4678078855195551</v>
+      </c>
+      <c r="K29" t="n">
+        <v>21.84864891483663</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.778585177206025</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.1605390642014986</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.250066115254011</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.152828954222077</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.138059701492537</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.04131207411197968</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.04409124505939773</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.03636401596596817</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0324707080157398</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.309520414194458</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.195937732900393</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.382104681011328</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.686825077105385</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.4347379486891416</v>
+      </c>
+      <c r="K30" t="n">
+        <v>18.25182250035001</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.7695406532225193</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.1028745958256489</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.8004805834652523</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.8609403251888068</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.8605798481180013</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.04857634072051509</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.05278742235010458</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.04397792095753296</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.09313046509354157</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.825547171750038</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.4570653941713318</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.905872244295606</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6589387896653373</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4330724070450098</v>
+      </c>
+      <c r="K31" t="n">
+        <v>15.04773635691216</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.7794049731617081</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.1350136094584467</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.164569636621046</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.591490702079265</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.617787663372613</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.05891638989865644</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.06308044809432856</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.05287179104903238</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.1712626221335193</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.425048760661872</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.6954368815957629</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.277545364553216</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.656208186950393</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.4274119496180328</v>
+      </c>
+      <c r="K32" t="n">
+        <v>20.78161221713274</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.7736726334586376</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.08946176937282102</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.6233588821472831</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.9398978230948993</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9516586902178279</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024年报</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.05039555305484145</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.06496704092898535</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.05351667561003909</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.2554963615533771</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.07015106252515</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.104906738687041</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13.48328613937832</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.747143562809359</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.5051806002197646</v>
+      </c>
+      <c r="K33" t="n">
+        <v>25.11238185846562</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.7463630839618258</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.1311523751653144</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.8402764859979652</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.8953149731545473</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8627225932747771</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.03370295988542804</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.04640853162867319</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.03818401716725241</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.02782956134019206</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.124068626492563</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1710231695799171</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.022326662080686</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6595508477057112</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.4303359071881029</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10.98965628332549</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.7713917708296448</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.1280599719084546</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.8392176009790112</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.8851467614408393</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.8852821515083459</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.04407054381787778</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.05752819411939717</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.04686803060212064</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.09536448892355803</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.721629777055008</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.4415253825248583</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.525465137773236</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6591642499166194</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.3990078256317602</v>
+      </c>
+      <c r="K35" t="n">
+        <v>16.52181423937781</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.7746999978141917</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.07730912429234457</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.410085767991661</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.98755157811884</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.958200365173797</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.04822794370321126</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.06320859347003557</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0522597898161389</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.169241908606567</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.032092546982017</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.6925192426086088</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.640944499170297</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7070975527834842</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.4575486436031025</v>
+      </c>
+      <c r="K36" t="n">
+        <v>19.99244827219004</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.7791288305027085</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.08677544291209799</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.66790686550615</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.8325978873741895</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.8597850411982642</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025年报</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.03155110897258784</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.04998315983816797</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.041992822776736</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.1623899317214994</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5.925861724636579</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.9756915490992057</v>
+      </c>
+      <c r="H37" t="n">
+        <v>13.80801823974444</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7929708763563318</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.486757419666091</v>
+      </c>
+      <c r="K37" t="n">
+        <v>16.74847599030748</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.7074457130571555</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.08534846616047889</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.6007224646134921</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.2657957156292552</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.286244261749707</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.04408327806228829</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0646901855998876</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.05543035435079391</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.03817471999599696</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.112385122696767</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1976044731150867</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.777896128087994</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8105900193160495</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.4951354001704238</v>
+      </c>
+      <c r="K38" t="n">
+        <v>19.3231619725335</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.7071349284437026</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.1396826038901784</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.788099659935676</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.7257501852259276</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.7202924176050787</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.03157503519410321</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.05041871687959599</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.04319892816046138</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.06663644858407783</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.435920769071823</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.4402010208255526</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7.689762294827318</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7609436726170531</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.4755588714264564</v>
+      </c>
+      <c r="K39" t="n">
+        <v>20.2578625475158</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.7108134645173411</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.1320197603099452</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.179384665623795</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6985849925898193</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.6984751893967474</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0312719237910335</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.05104608465795657</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.04279205078106588</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.09769353606276993</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.734070310266429</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6478017626588143</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13.68683793778551</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8703236143817822</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.5512895211737189</v>
+      </c>
+      <c r="K40" t="n">
+        <v>17.69344739644574</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.7135038944479862</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.1327438534246196</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.5251672595923236</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.5441451482514845</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.5108021796204849</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/002594_比亚迪_财务数据.xlsx
+++ b/data/002594_比亚迪_财务数据.xlsx
@@ -40545,7 +40545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40624,6 +40624,21 @@
           <t>净利润增长率</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>有息负债率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>经营现金流/营收</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>权益乘数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40676,6 +40691,15 @@
       <c r="P2" t="n">
         <v>-0.8361963440955968</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0.3434575691139511</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.06176902849642402</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.389806954472674</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40728,6 +40752,15 @@
       <c r="P3" t="n">
         <v>1.750602130461229</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.3635930504784984</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.03176893925447332</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.495219500990554</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40780,6 +40813,15 @@
       <c r="P4" t="n">
         <v>0.608563477621304</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.2765673068307398</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.03886106982093825</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.648394241417497</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40832,6 +40874,15 @@
       <c r="P5" t="n">
         <v>0.2380080727133376</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.3173010516622777</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0621160223818597</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.23792815067995</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40884,6 +40935,15 @@
       <c r="P6" t="n">
         <v>-0.8410868069057641</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0.3420854803657586</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.114890437380958</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.813907424857214</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40936,6 +40996,15 @@
       <c r="P7" t="n">
         <v>1.770997202335397</v>
       </c>
+      <c r="Q7" t="n">
+        <v>0.3568868507496666</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.07704667098764528</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.921385679537853</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40988,6 +41057,15 @@
       <c r="P8" t="n">
         <v>0.5988994823946281</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0.3415752027584867</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.00941394219717759</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.044711014176663</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41040,6 +41118,15 @@
       <c r="P9" t="n">
         <v>0.02724388323332017</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.3042436951035868</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.09629024807229776</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.524964672633066</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41092,6 +41179,15 @@
       <c r="P10" t="n">
         <v>-0.9257236601050618</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0.3264926192777436</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.006589169144174053</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.308610571070371</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41144,6 +41240,15 @@
       <c r="P11" t="n">
         <v>2.310205534165465</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0.3391480263673764</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.02690627843326052</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.527837713231904</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41196,6 +41301,15 @@
       <c r="P12" t="n">
         <v>1.454537656642966</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0.3190809336414933</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.07473478199234747</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.526276179812405</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41248,6 +41362,15 @@
       <c r="P13" t="n">
         <v>-0.01271811129873368</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0.3628873145848028</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1153997999491508</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.446707304182376</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41300,6 +41423,15 @@
       <c r="P14" t="n">
         <v>-0.5806715601855151</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.328131129731524</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.01346351985049157</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.518359257489692</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41352,6 +41484,15 @@
       <c r="P15" t="n">
         <v>0.8551621446105051</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.3641333706808587</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.03320775868968649</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.526680661151193</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41404,6 +41545,15 @@
       <c r="P16" t="n">
         <v>0.1495729555070477</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0.3663293412569492</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.04085404588871816</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.488543169898983</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41456,6 +41606,15 @@
       <c r="P17" t="n">
         <v>2.173849828587834</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.2558888054244168</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2898701743948447</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.534426978935894</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41508,6 +41667,15 @@
       <c r="P18" t="n">
         <v>-0.9464632555936909</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0.3736824778039642</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2514922091280949</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.374116195010139</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41560,6 +41728,15 @@
       <c r="P19" t="n">
         <v>6.40267045172191</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.3406666801594851</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2568137711418078</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.297890802296088</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41612,6 +41789,15 @@
       <c r="P20" t="n">
         <v>1.05665171478164</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.3024507238349788</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2729221233674459</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.29288044842299</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -41664,6 +41850,15 @@
       <c r="P21" t="n">
         <v>-0.1906629121818996</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.1148725404016499</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3028882880658373</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.111181234879562</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -41716,6 +41911,15 @@
       <c r="P22" t="n">
         <v>-0.8711828246454864</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.2293548055569209</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.003464101286613569</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.758551407053139</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -41768,6 +41972,15 @@
       <c r="P23" t="n">
         <v>2.54322260748417</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0.1803808968348325</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.1064747473191514</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.743154267429697</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -41820,6 +42033,15 @@
       <c r="P24" t="n">
         <v>0.8205189943952051</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.1694942845458408</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.2195294603590638</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.053897080221166</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41872,6 +42094,15 @@
       <c r="P25" t="n">
         <v>4.37323614465214</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0.03890163426551196</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3321175991730522</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.448036098676921</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -41924,6 +42155,15 @@
       <c r="P26" t="n">
         <v>-0.9485403574664271</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0.08334016664879491</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1785703997676924</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.308195524023162</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -41976,6 +42216,15 @@
       <c r="P27" t="n">
         <v>3.314967471558184</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.08685245835296566</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.2867391803948458</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.580856855986502</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -42028,6 +42277,15 @@
       <c r="P28" t="n">
         <v>1.539540966801046</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0.05629107221201647</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3400864141583536</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.157783327155316</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -42080,6 +42338,15 @@
       <c r="P29" t="n">
         <v>2.138059701492537</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0.05597544250001472</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.2817876032428023</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.895526258915064</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -42132,6 +42399,15 @@
       <c r="P30" t="n">
         <v>-0.8605798481180013</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.05862333052459957</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.1203758482478116</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.73366673300051</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -42184,6 +42460,15 @@
       <c r="P31" t="n">
         <v>1.617787663372613</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0.04198885868324049</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.315122614358791</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.93985760366353</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -42236,6 +42521,15 @@
       <c r="P32" t="n">
         <v>0.9516586902178279</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0.04046797361712096</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.2317448050267205</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.79980131838344</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -42288,6 +42582,15 @@
       <c r="P33" t="n">
         <v>0.8627225932747771</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0.0390422745214181</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1717328251137747</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.228619548612423</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -42340,6 +42643,15 @@
       <c r="P34" t="n">
         <v>-0.8852821515083459</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0.0529445959184637</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.08186041347656429</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.736767069676428</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -42392,6 +42704,15 @@
       <c r="P35" t="n">
         <v>1.958200365173797</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0.04286078587093531</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.04708316927033969</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.806074782718315</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -42444,6 +42765,15 @@
       <c r="P36" t="n">
         <v>0.8597850411982642</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0.05250830869075969</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.1120415191668031</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.91605665693224</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -42496,6 +42826,15 @@
       <c r="P37" t="n">
         <v>0.286244261749707</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0.1250393219648535</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.07355544468892138</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.588386965790275</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -42548,6 +42887,15 @@
       <c r="P38" t="n">
         <v>-0.7202924176050787</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0.03745864201863831</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.05036967266017051</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.601831497122484</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -42600,6 +42948,15 @@
       <c r="P39" t="n">
         <v>0.6984751893967474</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0.03684085530334628</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.08573830726159426</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.645421810256455</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -42651,6 +43008,15 @@
       </c>
       <c r="P40" t="n">
         <v>0.5108021796204849</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.09765667877040773</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.07213047003922785</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.673604464085698</v>
       </c>
     </row>
   </sheetData>
